--- a/results/Int Task Remove ACC 0.1/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.1/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.002354379227315477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03828438311119252</v>
+        <v>0.03829976978163591</v>
       </c>
       <c r="F3" t="n">
         <v>-0.0007549379507898878</v>
@@ -1175,7 +1175,7 @@
         <v>0.02250333310451026</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01979628777108319</v>
+        <v>0.0197926368035768</v>
       </c>
       <c r="L3" t="n">
         <v>0.0197888330759237</v>
@@ -1184,10 +1184,10 @@
         <v>0.009464336052702313</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04913034540761724</v>
+        <v>0.04911886224043246</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03070831299257305</v>
+        <v>0.03070065602473231</v>
       </c>
       <c r="P3" t="n">
         <v>0.01382415583330402</v>
@@ -1196,7 +1196,7 @@
         <v>0.005906125275081062</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01332472900007375</v>
+        <v>0.01333224246275201</v>
       </c>
       <c r="S3" t="n">
         <v>0.3210699299735382</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1139391910562481</v>
+        <v>0.1139428580896181</v>
       </c>
       <c r="AK3" t="n">
         <v>0.1148447695106562</v>
@@ -1289,7 +1289,7 @@
         <v>0.01175795560205722</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.006979419005859093</v>
+        <v>-0.006979280864191045</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0001756432711165578</v>
@@ -1298,7 +1298,7 @@
         <v>-0.001195196905570354</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01607247263595533</v>
+        <v>0.01607633513112721</v>
       </c>
       <c r="BA3" t="n">
         <v>0.007484872210896137</v>
@@ -1340,7 +1340,7 @@
         <v>0.0219744101227302</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.007484872210896137</v>
+        <v>0.007488539244266142</v>
       </c>
       <c r="BO3" t="n">
         <v>0.01481657628311573</v>
@@ -1376,7 +1376,7 @@
         <v>-3.2684531367515e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-3.64767194600446e-05</v>
+        <v>-3.280968609004065e-05</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0003101486065340453</v>
@@ -1394,7 +1394,7 @@
         <v>0.00277422139118248</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0005272981566555951</v>
+        <v>-0.0005308069285854186</v>
       </c>
       <c r="CG3" t="n">
         <v>0.01488824211741348</v>
@@ -1428,7 +1428,7 @@
         <v>0.03211523974640484</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0490882294791565</v>
+        <v>0.04909968796845914</v>
       </c>
       <c r="F4" t="n">
         <v>0.003984534445841506</v>
@@ -1446,7 +1446,7 @@
         <v>0.03445007918216039</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01588359871606506</v>
+        <v>0.01588698006751719</v>
       </c>
       <c r="L4" t="n">
         <v>0.01588333479159743</v>
@@ -1455,10 +1455,10 @@
         <v>0.02397956922919125</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05747755619600228</v>
+        <v>0.05747749683011788</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04563982435951972</v>
+        <v>0.04561718829227548</v>
       </c>
       <c r="P4" t="n">
         <v>0.01518126065741313</v>
@@ -1467,7 +1467,7 @@
         <v>0.0145185162762725</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01983844556135708</v>
+        <v>0.01983461683126641</v>
       </c>
       <c r="S4" t="n">
         <v>0.1046784233810915</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.06327013132360157</v>
+        <v>0.06326326211402898</v>
       </c>
       <c r="AK4" t="n">
         <v>0.05554662179212089</v>
@@ -1560,7 +1560,7 @@
         <v>0.01568745940195247</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01138641599269608</v>
+        <v>0.01139200383759235</v>
       </c>
       <c r="AX4" t="n">
         <v>0.002132967898700889</v>
@@ -1569,7 +1569,7 @@
         <v>0.03700936427548869</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02700341803254043</v>
+        <v>0.02700451274289753</v>
       </c>
       <c r="BA4" t="n">
         <v>0.01485768294954543</v>
@@ -1611,7 +1611,7 @@
         <v>0.03365316994559718</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01485768294954543</v>
+        <v>0.01485657005827951</v>
       </c>
       <c r="BO4" t="n">
         <v>0.01776280488787962</v>
@@ -1647,7 +1647,7 @@
         <v>0.0008353739065218314</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0008389217975488248</v>
+        <v>0.0008446804615932655</v>
       </c>
       <c r="CA4" t="n">
         <v>0.001236251647024049</v>
@@ -1665,7 +1665,7 @@
         <v>0.006873412263434441</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.02784107833035459</v>
+        <v>0.02784172405113429</v>
       </c>
       <c r="CG4" t="n">
         <v>0.03491180425461593</v>
@@ -1726,7 +1726,7 @@
         <v>-0.03008883738895329</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02214637846037169</v>
+        <v>-0.02218430034129698</v>
       </c>
       <c r="O5" t="n">
         <v>-0.009063329541145304</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.007260726072607271</v>
+        <v>0.00729739640630731</v>
       </c>
       <c r="AK5" t="n">
         <v>0.02724605793912725</v>
@@ -1988,7 +1988,7 @@
         <v>0.003957764180198511</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008108547184653625</v>
+        <v>0.008081164928355708</v>
       </c>
       <c r="L6" t="n">
         <v>0.008081164928355708</v>
@@ -1997,7 +1997,7 @@
         <v>-0.004031075983474086</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008366005809616012</v>
+        <v>0.008356349571686308</v>
       </c>
       <c r="O6" t="n">
         <v>0.0111080616833613</v>
@@ -2009,7 +2009,7 @@
         <v>-0.006642300776262333</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003433746989156758</v>
+        <v>0.00344287440792273</v>
       </c>
       <c r="S6" t="n">
         <v>0.2833472322358407</v>
@@ -2207,7 +2207,7 @@
         <v>-0.001789493834125919</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.005009792858870011</v>
+        <v>-0.005036108648343693</v>
       </c>
       <c r="CG6" t="n">
         <v>-0.003133549482247269</v>
@@ -2241,7 +2241,7 @@
         <v>0.003789741753733078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02423313985771603</v>
+        <v>0.0242712060984813</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001326353425131543</v>
@@ -2280,7 +2280,7 @@
         <v>0.005718082945276098</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004517317732192383</v>
+        <v>0.004536630208051789</v>
       </c>
       <c r="S7" t="n">
         <v>0.3107089149506804</v>
@@ -2373,7 +2373,7 @@
         <v>0.002696904376983378</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.004803771223008763</v>
+        <v>-0.004822106389858782</v>
       </c>
       <c r="AX7" t="n">
         <v>0.0005333040545767054</v>
@@ -2424,7 +2424,7 @@
         <v>0.006143513977030829</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003354293324069241</v>
+        <v>0.00337262849091926</v>
       </c>
       <c r="BO7" t="n">
         <v>0.01303651259813226</v>
@@ -2512,7 +2512,7 @@
         <v>0.00796002891781509</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0424269309776166</v>
+        <v>0.04244492440875888</v>
       </c>
       <c r="F8" t="n">
         <v>0.001235042995669886</v>
@@ -2653,7 +2653,7 @@
         <v>-0.001603663780738049</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.02355213186085555</v>
+        <v>0.02356178809878525</v>
       </c>
       <c r="BA8" t="n">
         <v>0.00961653640083115</v>
@@ -2783,7 +2783,7 @@
         <v>0.07237442922374429</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1588820826952527</v>
+        <v>0.1589203675344564</v>
       </c>
       <c r="F9" t="n">
         <v>0.004571428571428515</v>
@@ -2810,10 +2810,10 @@
         <v>0.04192688499619195</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1612557427258806</v>
+        <v>0.1612174578866769</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1521439509954058</v>
+        <v>0.1520673813169985</v>
       </c>
       <c r="P9" t="n">
         <v>0.04134762633996938</v>
@@ -2915,7 +2915,7 @@
         <v>0.03986065273193986</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.008295281582952818</v>
+        <v>0.008333333333333337</v>
       </c>
       <c r="AX9" t="n">
         <v>0.003244495944380033</v>
@@ -3002,7 +3002,7 @@
         <v>0.00113678034470116</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.00113678034470116</v>
+        <v>0.0011734506784012</v>
       </c>
       <c r="CA9" t="n">
         <v>0.00176110260336908</v>
